--- a/data/P2P_members_list.xlsx
+++ b/data/P2P_members_list.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11010"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="11214"/>
   <workbookPr showInkAnnotation="0" autoCompressPictures="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enriquemontes/p2p/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/enrique.montes/Documents/p2p/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B11E4C9D-FD23-F544-AC00-E4CFD8E5B45E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DD5A229-6909-0943-A827-C30D7B45638A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="340" yWindow="2840" windowWidth="33120" windowHeight="16600" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="54160" yWindow="620" windowWidth="45220" windowHeight="25480" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="P2P_members" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" concurrentCalc="0"/>
   <extLst>
     <ext xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" uri="{7523E5D3-25F3-A5E0-1632-64F254C22452}">
       <mx:ArchID Flags="2"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="245" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="152">
   <si>
     <t>Country</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Andrew.Cooper@dfo-mpo.gc.ca</t>
   </si>
   <si>
-    <t>marques@ib.usp.br</t>
-  </si>
-  <si>
     <t>guca@usp.br</t>
   </si>
   <si>
@@ -156,9 +153,6 @@
     <t>inti.keith@fcdarwin.org.ec</t>
   </si>
   <si>
-    <t>Costa Rica</t>
-  </si>
-  <si>
     <t>Kristin Wilson Grimes</t>
   </si>
   <si>
@@ -234,12 +228,6 @@
     <t xml:space="preserve">ruisea@gmail.com </t>
   </si>
   <si>
-    <t>juan.azofeifa@ucr.ac.cr</t>
-  </si>
-  <si>
-    <t>DS</t>
-  </si>
-  <si>
     <t>SG</t>
   </si>
   <si>
@@ -261,18 +249,12 @@
     <t>gabrielle.canonico@noaa.gov</t>
   </si>
   <si>
-    <t>[Abigail Benson](https://oceanexpert.org/expert/25483){target="_blank"}</t>
-  </si>
-  <si>
     <t>[Ana Carolina Mazzuco](https://oceanexpert.org/expert/34916){target="_blank"}</t>
   </si>
   <si>
     <t>[Andrew Cooper](https://profils-profiles.science.gc.ca/en/profile/andrew-cooper){target="_blank"}</t>
   </si>
   <si>
-    <t>[Antonio Marques](https://oceanexpert.org/expert/28123){target="_blank"}</t>
-  </si>
-  <si>
     <t>[Augusto Flores](http://cebimar.usp.br/pt/quem-somos/equipe-academica){target="_blank"}</t>
   </si>
   <si>
@@ -333,9 +315,6 @@
     <t>[Jonathan Lefcheck](https://oceanexpert.org/expert/37241){target="_blank"}</t>
   </si>
   <si>
-    <t>[Juan Azofeifa](https://oceanexpert.org/expert/34929){target="_blank"}</t>
-  </si>
-  <si>
     <t>[Luis Escudero](https://www.gob.pe/institucion/imarpe/funcionarios/30904-luis-orlando-escudero-herrera){target="_blank"}</t>
   </si>
   <si>
@@ -366,9 +345,6 @@
     <t>[Yasmina Shah Esmaeili](https://oceanexpert.org/expert/35244){target="_blank"}</t>
   </si>
   <si>
-    <t>[OBIS-USA / USGS](https://www.usgs.gov/core-science-systems/science-analytics-and-synthesis/obis-usa){target="_blank"}</t>
-  </si>
-  <si>
     <t>[U. West Indies](https://sta.uwi.edu/fst/lifesciences/){target="_blank"}</t>
   </si>
   <si>
@@ -435,9 +411,6 @@
     <t>[Charles Darwin F.](https://www.darwinfoundation.org/en/){target="_blank"}</t>
   </si>
   <si>
-    <t>[CIMAR](http://www.cimar.ucr.ac.cr/index.php){target="_blank"}</t>
-  </si>
-  <si>
     <t>[CMES - UVI](https://www.uvi.edu/research/center-for-marine-environmental-studies/about-cmes/default.aspx){target="_blank"}</t>
   </si>
   <si>
@@ -465,9 +438,6 @@
     <t>[UNICAMP](https://www.ib.unicamp.br/){target="_blank"}</t>
   </si>
   <si>
-    <t>alana.jute@gmail.com</t>
-  </si>
-  <si>
     <t>[Jose H. Muelbert](https://oceanexpert.org/expert/10272){target="_blank"}</t>
   </si>
   <si>
@@ -477,27 +447,6 @@
     <t>jmuelbert@furg.br</t>
   </si>
   <si>
-    <t>marga.copertino@gmail.com</t>
-  </si>
-  <si>
-    <t>[Margareth Copertino](https://furg.academia.edu/Mcopertino){target="_blank"}</t>
-  </si>
-  <si>
-    <t>[Eduardo Secchi](https://io.furg.br/servidores/27-docentes/nucleo-de-oceanografia-biologica/229-eduardo-resende-secchi){target="_blank"}</t>
-  </si>
-  <si>
-    <t>edu.secchi@furg.br</t>
-  </si>
-  <si>
-    <t>[Marianna Lanari](https://oceanexpert.org/expert/mlanari){target="_blank"}</t>
-  </si>
-  <si>
-    <t>SG/SB</t>
-  </si>
-  <si>
-    <t>marianna.lanari@gmail.com</t>
-  </si>
-  <si>
     <t>Melissa Miner</t>
   </si>
   <si>
@@ -526,6 +475,12 @@
   </si>
   <si>
     <t>scerdeira@conabio.gob.mx</t>
+  </si>
+  <si>
+    <t>[Gonzalo Bravo](https://oceanexpert.org/expert/39346){target="_blank"}</t>
+  </si>
+  <si>
+    <t>gonzalobravoargentina@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -561,9 +516,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -903,7 +857,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.83203125" bestFit="1" customWidth="1"/>
@@ -913,7 +867,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -930,118 +884,118 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>146</v>
+        <v>5</v>
+      </c>
+      <c r="E2" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>4</v>
       </c>
       <c r="C3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="D3" t="s">
         <v>5</v>
       </c>
       <c r="E3" t="s">
-        <v>65</v>
+        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="D4" t="s">
         <v>5</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="D5" t="s">
         <v>5</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B6" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C6" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="D6" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>82</v>
+        <v>141</v>
       </c>
       <c r="B7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>117</v>
+        <v>142</v>
       </c>
       <c r="D7" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C8" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="D8" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E8" t="s">
         <v>13</v>
@@ -1049,424 +1003,424 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>158</v>
+        <v>14</v>
       </c>
       <c r="B9" t="s">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>112</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="E9" t="s">
-        <v>160</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C10" t="s">
-        <v>119</v>
+        <v>113</v>
       </c>
       <c r="D10" t="s">
         <v>5</v>
       </c>
       <c r="E10" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>15</v>
+        <v>80</v>
       </c>
       <c r="B11" t="s">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="C11" t="s">
-        <v>120</v>
+        <v>114</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="B12" t="s">
-        <v>4</v>
+        <v>53</v>
       </c>
       <c r="C12" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="D12" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>122</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
         <v>5</v>
       </c>
       <c r="E13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="B14" t="s">
-        <v>55</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>56</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>117</v>
       </c>
       <c r="D15" t="s">
-        <v>5</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
-        <v>23</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>152</v>
+        <v>85</v>
       </c>
       <c r="B16" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C16" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="D16" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E16" t="s">
-        <v>153</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B18" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>67</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B21" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C21" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="D21" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="E21" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B22" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="D22" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E22" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B23" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C23" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
         <v>5</v>
       </c>
       <c r="E23" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="D24" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="E24" t="s">
-        <v>33</v>
+        <v>151</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="D25" t="s">
-        <v>76</v>
+        <v>5</v>
       </c>
       <c r="E25" t="s">
-        <v>77</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
-        <v>98</v>
+        <v>38</v>
       </c>
       <c r="B26" t="s">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="C26" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="D26" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="B27" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="D27" t="s">
-        <v>5</v>
+        <v>56</v>
       </c>
       <c r="E27" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>95</v>
       </c>
       <c r="B28" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="D28" t="s">
-        <v>16</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>40</v>
+        <v>59</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
-        <v>100</v>
+        <v>137</v>
       </c>
       <c r="B29" t="s">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="C29" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E29" t="s">
-        <v>42</v>
+        <v>139</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
-        <v>101</v>
+        <v>42</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>43</v>
       </c>
       <c r="C30" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="D30" t="s">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="E30" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="B31" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="C31" t="s">
-        <v>148</v>
+        <v>129</v>
       </c>
       <c r="D31" t="s">
+        <v>68</v>
+      </c>
+      <c r="E31" t="s">
         <v>58</v>
-      </c>
-      <c r="E31" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B32" t="s">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="C32" t="s">
-        <v>136</v>
+        <v>130</v>
       </c>
       <c r="D32" t="s">
-        <v>58</v>
+        <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>69</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="B33" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="D33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E33" t="s">
         <v>46</v>
@@ -1474,16 +1428,16 @@
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="D34" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E34" t="s">
         <v>60</v>
@@ -1491,16 +1445,16 @@
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="B35" t="s">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="C35" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="D35" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E35" t="s">
         <v>47</v>
@@ -1508,33 +1462,33 @@
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B36" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C36" t="s">
-        <v>148</v>
+        <v>134</v>
       </c>
       <c r="D36" t="s">
-        <v>71</v>
+        <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>150</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B37" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="C37" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="D37" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E37" t="s">
         <v>48</v>
@@ -1542,211 +1496,126 @@
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>53</v>
       </c>
       <c r="C38" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="D38" t="s">
-        <v>72</v>
+        <v>15</v>
       </c>
       <c r="E38" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="B39" t="s">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="C39" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="D39" t="s">
-        <v>155</v>
+        <v>5</v>
       </c>
       <c r="E39" t="s">
-        <v>156</v>
+        <v>49</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="B40" t="s">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="C40" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="D40" t="s">
         <v>5</v>
       </c>
       <c r="E40" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>157</v>
+        <v>104</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>30</v>
       </c>
       <c r="C41" t="s">
-        <v>143</v>
+        <v>122</v>
       </c>
       <c r="D41" t="s">
         <v>5</v>
       </c>
       <c r="E41" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>108</v>
+        <v>50</v>
       </c>
       <c r="B42" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="C42" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="D42" t="s">
-        <v>58</v>
+        <v>146</v>
       </c>
       <c r="E42" t="s">
-        <v>50</v>
+        <v>145</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>109</v>
+        <v>147</v>
       </c>
       <c r="B43" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C43" t="s">
-        <v>123</v>
+        <v>148</v>
       </c>
       <c r="D43" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="E43" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B44" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="C44" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="D44" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E44" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" t="s">
-        <v>74</v>
-      </c>
-      <c r="B45" t="s">
-        <v>11</v>
-      </c>
-      <c r="C45" t="s">
-        <v>143</v>
-      </c>
-      <c r="D45" t="s">
-        <v>5</v>
-      </c>
-      <c r="E45" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" t="s">
-        <v>111</v>
-      </c>
-      <c r="B46" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" t="s">
-        <v>130</v>
-      </c>
-      <c r="D46" t="s">
-        <v>5</v>
-      </c>
-      <c r="E46" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" t="s">
-        <v>52</v>
-      </c>
-      <c r="B47" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47" t="s">
-        <v>161</v>
-      </c>
-      <c r="D47" t="s">
-        <v>163</v>
-      </c>
-      <c r="E47" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" t="s">
-        <v>164</v>
-      </c>
-      <c r="B48" t="s">
-        <v>55</v>
-      </c>
-      <c r="C48" t="s">
-        <v>165</v>
-      </c>
-      <c r="D48" t="s">
-        <v>5</v>
-      </c>
-      <c r="E48" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" t="s">
-        <v>112</v>
-      </c>
-      <c r="B49" t="s">
-        <v>4</v>
-      </c>
-      <c r="C49" t="s">
-        <v>145</v>
-      </c>
-      <c r="D49" t="s">
-        <v>16</v>
-      </c>
-      <c r="E49" t="s">
-        <v>53</v>
-      </c>
-    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E47" r:id="rId1" xr:uid="{249375E2-EDD7-4DDC-B62E-FE3D76DCC9C0}"/>
+    <hyperlink ref="E42" r:id="rId1" xr:uid="{249375E2-EDD7-4DDC-B62E-FE3D76DCC9C0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <extLst>
